--- a/Configs/GameConfig/Datas/itemdef.xlsx
+++ b/Configs/GameConfig/Datas/itemdef.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -862,7 +862,6 @@
       <c r="F5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>1</v>
       </c>
@@ -895,14 +894,12 @@
       <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
-      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -922,7 +919,6 @@
       <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>1</v>
       </c>
@@ -955,14 +951,12 @@
       <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
-      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -982,7 +976,6 @@
       <c r="F7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>0</v>
       </c>
@@ -1015,14 +1008,12 @@
       <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
-      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -1042,7 +1033,6 @@
       <c r="F8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>1</v>
       </c>
@@ -1075,14 +1065,12 @@
       <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
-      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -1102,7 +1090,6 @@
       <c r="F9" t="n">
         <v>4</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>0</v>
       </c>
@@ -1135,14 +1122,12 @@
       <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
-      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" t="n">
@@ -1162,7 +1147,6 @@
       <c r="F10" t="n">
         <v>5</v>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>0</v>
       </c>
@@ -1195,14 +1179,12 @@
       <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
-      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" t="n">
@@ -1222,7 +1204,6 @@
       <c r="F11" t="n">
         <v>6</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>0</v>
       </c>
@@ -1255,14 +1236,12 @@
       <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
-      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" t="n">
@@ -1282,7 +1261,6 @@
       <c r="F12" t="n">
         <v>2</v>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>0</v>
       </c>
@@ -1315,14 +1293,69 @@
       <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
-      <c r="U12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>30101</v>
+      </c>
+      <c r="C13" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D13" t="n">
+        <v>210101</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>icon_avatar_event</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Configs/GameConfig/Datas/itemdef.xlsx
+++ b/Configs/GameConfig/Datas/itemdef.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1357,6 +1357,1260 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>31001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>111001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>211001</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>31002</v>
+      </c>
+      <c r="C15" t="n">
+        <v>111002</v>
+      </c>
+      <c r="D15" t="n">
+        <v>211002</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>31003</v>
+      </c>
+      <c r="C16" t="n">
+        <v>111003</v>
+      </c>
+      <c r="D16" t="n">
+        <v>211003</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>31004</v>
+      </c>
+      <c r="C17" t="n">
+        <v>111004</v>
+      </c>
+      <c r="D17" t="n">
+        <v>211004</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>31005</v>
+      </c>
+      <c r="C18" t="n">
+        <v>111005</v>
+      </c>
+      <c r="D18" t="n">
+        <v>211005</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>31006</v>
+      </c>
+      <c r="C19" t="n">
+        <v>111006</v>
+      </c>
+      <c r="D19" t="n">
+        <v>211006</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>31007</v>
+      </c>
+      <c r="C20" t="n">
+        <v>111007</v>
+      </c>
+      <c r="D20" t="n">
+        <v>211007</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>31008</v>
+      </c>
+      <c r="C21" t="n">
+        <v>111008</v>
+      </c>
+      <c r="D21" t="n">
+        <v>211008</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>31009</v>
+      </c>
+      <c r="C22" t="n">
+        <v>111009</v>
+      </c>
+      <c r="D22" t="n">
+        <v>211009</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>31010</v>
+      </c>
+      <c r="C23" t="n">
+        <v>111010</v>
+      </c>
+      <c r="D23" t="n">
+        <v>211010</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>31011</v>
+      </c>
+      <c r="C24" t="n">
+        <v>111011</v>
+      </c>
+      <c r="D24" t="n">
+        <v>211011</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>31012</v>
+      </c>
+      <c r="C25" t="n">
+        <v>111012</v>
+      </c>
+      <c r="D25" t="n">
+        <v>211012</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>31013</v>
+      </c>
+      <c r="C26" t="n">
+        <v>111013</v>
+      </c>
+      <c r="D26" t="n">
+        <v>211013</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>31014</v>
+      </c>
+      <c r="C27" t="n">
+        <v>111014</v>
+      </c>
+      <c r="D27" t="n">
+        <v>211014</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>31015</v>
+      </c>
+      <c r="C28" t="n">
+        <v>111015</v>
+      </c>
+      <c r="D28" t="n">
+        <v>211015</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>31016</v>
+      </c>
+      <c r="C29" t="n">
+        <v>111016</v>
+      </c>
+      <c r="D29" t="n">
+        <v>211016</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>31017</v>
+      </c>
+      <c r="C30" t="n">
+        <v>111017</v>
+      </c>
+      <c r="D30" t="n">
+        <v>211017</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>31018</v>
+      </c>
+      <c r="C31" t="n">
+        <v>111018</v>
+      </c>
+      <c r="D31" t="n">
+        <v>211018</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>31019</v>
+      </c>
+      <c r="C32" t="n">
+        <v>111019</v>
+      </c>
+      <c r="D32" t="n">
+        <v>211019</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>31020</v>
+      </c>
+      <c r="C33" t="n">
+        <v>111020</v>
+      </c>
+      <c r="D33" t="n">
+        <v>211020</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>31021</v>
+      </c>
+      <c r="C34" t="n">
+        <v>111021</v>
+      </c>
+      <c r="D34" t="n">
+        <v>211021</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>31022</v>
+      </c>
+      <c r="C35" t="n">
+        <v>111022</v>
+      </c>
+      <c r="D35" t="n">
+        <v>211022</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>icon_item_mat</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
